--- a/public/templates/master_order_template.xlsx
+++ b/public/templates/master_order_template.xlsx
@@ -397,12 +397,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:G3"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -410,12 +413,21 @@
         <v>订单号</v>
       </c>
       <c r="B1" t="str">
-        <v>母件料号</v>
+        <v>物料代码</v>
       </c>
       <c r="C1" t="str">
+        <v>物料名称</v>
+      </c>
+      <c r="D1" t="str">
+        <v>规格型号</v>
+      </c>
+      <c r="E1" t="str">
         <v>客户</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
+        <v>数量</v>
+      </c>
+      <c r="G1" t="str">
         <v>备注</v>
       </c>
     </row>
@@ -427,10 +439,19 @@
         <v>M-100</v>
       </c>
       <c r="C2" t="str">
+        <v>成品总成A</v>
+      </c>
+      <c r="D2" t="str">
+        <v>标准版</v>
+      </c>
+      <c r="E2" t="str">
         <v>测试客户A</v>
       </c>
-      <c r="D2" t="str">
-        <v>总包订单一行对应一张总包标签</v>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>母件代码对应BOM母件物料代码</v>
       </c>
     </row>
     <row r="3">
@@ -441,15 +462,24 @@
         <v>M-100</v>
       </c>
       <c r="C3" t="str">
+        <v>成品总成A</v>
+      </c>
+      <c r="D3" t="str">
+        <v>标准版</v>
+      </c>
+      <c r="E3" t="str">
         <v>测试客户B</v>
       </c>
-      <c r="D3" t="str">
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>